--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122531909</v>
+        <v>122528135</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323645</v>
+        <v>323509</v>
       </c>
       <c r="R2" t="n">
-        <v>6457645</v>
+        <v>6458215</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,6 +768,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +790,7 @@
         <v>122530418</v>
       </c>
       <c r="B3" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122532617</v>
+        <v>122531909</v>
       </c>
       <c r="B4" t="n">
-        <v>94996</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323263</v>
+        <v>323645</v>
       </c>
       <c r="R4" t="n">
-        <v>6457903</v>
+        <v>6457645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122531191</v>
+        <v>122530740</v>
       </c>
       <c r="B5" t="n">
         <v>80613</v>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528135</v>
+        <v>122527902</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,34 +1115,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1142,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323509</v>
+        <v>323476</v>
       </c>
       <c r="R6" t="n">
-        <v>6458215</v>
+        <v>6458188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122529772</v>
+        <v>122532617</v>
       </c>
       <c r="B7" t="n">
-        <v>94996</v>
+        <v>95009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323743</v>
+        <v>323263</v>
       </c>
       <c r="R7" t="n">
-        <v>6458096</v>
+        <v>6457903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122527769</v>
+        <v>122527780</v>
       </c>
       <c r="B8" t="n">
-        <v>94996</v>
+        <v>94649</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1331,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122527902</v>
+        <v>122527769</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>95009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,46 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323476</v>
+        <v>323433</v>
       </c>
       <c r="R9" t="n">
-        <v>6458188</v>
+        <v>6458170</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122527780</v>
+        <v>122529772</v>
       </c>
       <c r="B10" t="n">
-        <v>94636</v>
+        <v>95009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,34 +1535,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323433</v>
+        <v>323743</v>
       </c>
       <c r="R10" t="n">
-        <v>6458170</v>
+        <v>6458096</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122531909</v>
+        <v>122530740</v>
       </c>
       <c r="B4" t="n">
-        <v>5193</v>
+        <v>80613</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,43 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R4" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122530740</v>
+        <v>122531909</v>
       </c>
       <c r="B5" t="n">
-        <v>80613</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,38 +1008,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R5" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122528135</v>
+        <v>122527780</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>94649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323509</v>
+        <v>323433</v>
       </c>
       <c r="R2" t="n">
-        <v>6458215</v>
+        <v>6458170</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122530418</v>
+        <v>122530740</v>
       </c>
       <c r="B3" t="n">
-        <v>95009</v>
+        <v>80613</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323793</v>
+        <v>323863</v>
       </c>
       <c r="R3" t="n">
-        <v>6457779</v>
+        <v>6457768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122530740</v>
+        <v>122532617</v>
       </c>
       <c r="B4" t="n">
-        <v>80613</v>
+        <v>95009</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323863</v>
+        <v>323263</v>
       </c>
       <c r="R4" t="n">
-        <v>6457768</v>
+        <v>6457903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122531909</v>
+        <v>122530418</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>95009</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323645</v>
+        <v>323793</v>
       </c>
       <c r="R5" t="n">
-        <v>6457645</v>
+        <v>6457779</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122527902</v>
+        <v>122528135</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,33 +1100,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1151,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323476</v>
+        <v>323509</v>
       </c>
       <c r="R6" t="n">
-        <v>6458188</v>
+        <v>6458215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122532617</v>
+        <v>122527769</v>
       </c>
       <c r="B7" t="n">
         <v>95009</v>
@@ -1249,14 +1236,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323263</v>
+        <v>323433</v>
       </c>
       <c r="R7" t="n">
-        <v>6457903</v>
+        <v>6458170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122527780</v>
+        <v>122531909</v>
       </c>
       <c r="B8" t="n">
-        <v>94649</v>
+        <v>5193</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323433</v>
+        <v>323645</v>
       </c>
       <c r="R8" t="n">
-        <v>6458170</v>
+        <v>6457645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122527769</v>
+        <v>122527902</v>
       </c>
       <c r="B9" t="n">
-        <v>95009</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1421,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323433</v>
+        <v>323476</v>
       </c>
       <c r="R9" t="n">
-        <v>6458170</v>
+        <v>6458188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122529772</v>
+        <v>122531091</v>
       </c>
       <c r="B10" t="n">
-        <v>95009</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,38 +1531,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323743</v>
+        <v>323863</v>
       </c>
       <c r="R10" t="n">
-        <v>6458096</v>
+        <v>6457768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122531091</v>
+        <v>122529772</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>95009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,43 +1638,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323863</v>
+        <v>323743</v>
       </c>
       <c r="R11" t="n">
-        <v>6457768</v>
+        <v>6458096</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122527780</v>
+        <v>122531909</v>
       </c>
       <c r="B2" t="n">
-        <v>94649</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323433</v>
+        <v>323645</v>
       </c>
       <c r="R2" t="n">
-        <v>6458170</v>
+        <v>6457645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122530740</v>
+        <v>122527902</v>
       </c>
       <c r="B3" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323863</v>
+        <v>323476</v>
       </c>
       <c r="R3" t="n">
-        <v>6457768</v>
+        <v>6458188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122532617</v>
+        <v>122527769</v>
       </c>
       <c r="B4" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323263</v>
+        <v>323433</v>
       </c>
       <c r="R4" t="n">
-        <v>6457903</v>
+        <v>6458170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +997,7 @@
         <v>122530418</v>
       </c>
       <c r="B5" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528135</v>
+        <v>122527780</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>94651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,43 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323509</v>
+        <v>323433</v>
       </c>
       <c r="R6" t="n">
-        <v>6458215</v>
+        <v>6458170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1185,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122527769</v>
+        <v>122532617</v>
       </c>
       <c r="B7" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,14 +1239,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323433</v>
+        <v>323263</v>
       </c>
       <c r="R7" t="n">
-        <v>6458170</v>
+        <v>6457903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122531909</v>
+        <v>122528135</v>
       </c>
       <c r="B8" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,39 +1321,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323645</v>
+        <v>323509</v>
       </c>
       <c r="R8" t="n">
-        <v>6457645</v>
+        <v>6458215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,6 +1398,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122527902</v>
+        <v>122531191</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,42 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323476</v>
+        <v>323863</v>
       </c>
       <c r="R9" t="n">
-        <v>6458188</v>
+        <v>6457768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
         <v>122529772</v>
       </c>
       <c r="B11" t="n">
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122531909</v>
+        <v>122527902</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,21 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323645</v>
+        <v>323476</v>
       </c>
       <c r="R2" t="n">
-        <v>6457645</v>
+        <v>6458188</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122527902</v>
+        <v>122531091</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -816,24 +819,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323476</v>
+        <v>323863</v>
       </c>
       <c r="R3" t="n">
-        <v>6458188</v>
+        <v>6457768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122527769</v>
+        <v>122530418</v>
       </c>
       <c r="B4" t="n">
         <v>95011</v>
@@ -928,14 +928,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323433</v>
+        <v>323793</v>
       </c>
       <c r="R4" t="n">
-        <v>6458170</v>
+        <v>6457779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122530418</v>
+        <v>122527769</v>
       </c>
       <c r="B5" t="n">
         <v>95011</v>
@@ -1030,14 +1035,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323793</v>
+        <v>323433</v>
       </c>
       <c r="R5" t="n">
-        <v>6457779</v>
+        <v>6458170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,11 +1075,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122527780</v>
+        <v>122532617</v>
       </c>
       <c r="B6" t="n">
-        <v>94651</v>
+        <v>95011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,34 +1117,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323433</v>
+        <v>323263</v>
       </c>
       <c r="R6" t="n">
-        <v>6458170</v>
+        <v>6457903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122532617</v>
+        <v>122531191</v>
       </c>
       <c r="B7" t="n">
-        <v>95011</v>
+        <v>80613</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323263</v>
+        <v>323863</v>
       </c>
       <c r="R7" t="n">
-        <v>6457903</v>
+        <v>6457768</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528135</v>
+        <v>122529772</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>95011</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,43 +1321,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323509</v>
+        <v>323743</v>
       </c>
       <c r="R8" t="n">
-        <v>6458215</v>
+        <v>6458096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1389,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122531191</v>
+        <v>122527780</v>
       </c>
       <c r="B9" t="n">
-        <v>80613</v>
+        <v>94651</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323863</v>
+        <v>323433</v>
       </c>
       <c r="R9" t="n">
-        <v>6457768</v>
+        <v>6458170</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531091</v>
+        <v>122528135</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,43 +1521,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323863</v>
+        <v>323509</v>
       </c>
       <c r="R10" t="n">
-        <v>6457768</v>
+        <v>6458215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122529772</v>
+        <v>122531909</v>
       </c>
       <c r="B11" t="n">
-        <v>95011</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,34 +1637,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323743</v>
+        <v>323645</v>
       </c>
       <c r="R11" t="n">
-        <v>6458096</v>
+        <v>6457645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122527902</v>
+        <v>122530740</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>80614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323476</v>
+        <v>323863</v>
       </c>
       <c r="R2" t="n">
-        <v>6458188</v>
+        <v>6457768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122531091</v>
+        <v>122530418</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>95012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,43 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323863</v>
+        <v>323793</v>
       </c>
       <c r="R3" t="n">
-        <v>6457768</v>
+        <v>6457779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122530418</v>
+        <v>122532617</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323793</v>
+        <v>323263</v>
       </c>
       <c r="R4" t="n">
-        <v>6457779</v>
+        <v>6457903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122527769</v>
+        <v>122527780</v>
       </c>
       <c r="B5" t="n">
-        <v>95011</v>
+        <v>94652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122532617</v>
+        <v>122527902</v>
       </c>
       <c r="B6" t="n">
-        <v>95011</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1100,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323263</v>
+        <v>323476</v>
       </c>
       <c r="R6" t="n">
-        <v>6457903</v>
+        <v>6458188</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122531191</v>
+        <v>122529772</v>
       </c>
       <c r="B7" t="n">
-        <v>80613</v>
+        <v>95012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323863</v>
+        <v>323743</v>
       </c>
       <c r="R7" t="n">
-        <v>6457768</v>
+        <v>6458096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122529772</v>
+        <v>122528135</v>
       </c>
       <c r="B8" t="n">
-        <v>95011</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,34 +1316,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323743</v>
+        <v>323509</v>
       </c>
       <c r="R8" t="n">
-        <v>6458096</v>
+        <v>6458215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,6 +1393,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1407,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122527780</v>
+        <v>122531909</v>
       </c>
       <c r="B9" t="n">
-        <v>94651</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,34 +1428,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323433</v>
+        <v>323645</v>
       </c>
       <c r="R9" t="n">
-        <v>6458170</v>
+        <v>6457645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122528135</v>
+        <v>122527769</v>
       </c>
       <c r="B10" t="n">
-        <v>8430</v>
+        <v>95012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,43 +1535,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323509</v>
+        <v>323433</v>
       </c>
       <c r="R10" t="n">
-        <v>6458215</v>
+        <v>6458170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1603,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122531909</v>
+        <v>122531091</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R11" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122531909</v>
+        <v>122527769</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>95012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,39 +1428,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323645</v>
+        <v>323433</v>
       </c>
       <c r="R9" t="n">
-        <v>6457645</v>
+        <v>6458170</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122527769</v>
+        <v>122531909</v>
       </c>
       <c r="B10" t="n">
-        <v>95012</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,34 +1530,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323433</v>
+        <v>323645</v>
       </c>
       <c r="R10" t="n">
-        <v>6458170</v>
+        <v>6457645</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,6 +1726,468 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122686633</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredfjället, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>323737</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6458105</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122686735</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5193</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bredfjället, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>323636</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6457620</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122686595</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bredfjället, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>323745</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6458102</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lite, vid myrkanten.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122686698</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bredfjället, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>323768</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6458043</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122530740</v>
       </c>
       <c r="B2" t="n">
-        <v>80614</v>
+        <v>80617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122530418</v>
+        <v>122528135</v>
       </c>
       <c r="B3" t="n">
-        <v>95012</v>
+        <v>8430</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323793</v>
+        <v>323509</v>
       </c>
       <c r="R3" t="n">
-        <v>6457779</v>
+        <v>6458215</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,17 +864,13 @@
           <t>2025-02-09</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122532617</v>
+        <v>122529772</v>
       </c>
       <c r="B4" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323263</v>
+        <v>323743</v>
       </c>
       <c r="R4" t="n">
-        <v>6457903</v>
+        <v>6458096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122527780</v>
+        <v>122531909</v>
       </c>
       <c r="B5" t="n">
-        <v>94652</v>
+        <v>5193</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1007,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323433</v>
+        <v>323645</v>
       </c>
       <c r="R5" t="n">
-        <v>6458170</v>
+        <v>6457645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1198,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122529772</v>
+        <v>122527769</v>
       </c>
       <c r="B7" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,14 +1244,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323743</v>
+        <v>323433</v>
       </c>
       <c r="R7" t="n">
-        <v>6458096</v>
+        <v>6458170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528135</v>
+        <v>122532617</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>95015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,43 +1326,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323509</v>
+        <v>323263</v>
       </c>
       <c r="R8" t="n">
-        <v>6458215</v>
+        <v>6457903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1394,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122527769</v>
+        <v>122530418</v>
       </c>
       <c r="B9" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323433</v>
+        <v>323793</v>
       </c>
       <c r="R9" t="n">
-        <v>6458170</v>
+        <v>6457779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1488,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531909</v>
+        <v>122531091</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,20 +1531,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1550,7 +1555,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1559,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R10" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122531091</v>
+        <v>122527780</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>94655</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,43 +1638,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323863</v>
+        <v>323433</v>
       </c>
       <c r="R11" t="n">
-        <v>6457768</v>
+        <v>6458170</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686633</v>
+        <v>122686735</v>
       </c>
       <c r="B12" t="n">
-        <v>56594</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,29 +1744,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323737</v>
+        <v>323636</v>
       </c>
       <c r="R12" t="n">
-        <v>6458105</v>
+        <v>6457620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1826,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686735</v>
+        <v>122686595</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>56594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,30 +1861,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1892,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323636</v>
+        <v>323745</v>
       </c>
       <c r="R13" t="n">
-        <v>6457620</v>
+        <v>6458102</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,7 +1942,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686595</v>
+        <v>122686633</v>
       </c>
       <c r="B14" t="n">
         <v>56594</v>
@@ -1998,7 +1998,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323745</v>
+        <v>323737</v>
       </c>
       <c r="R14" t="n">
-        <v>6458102</v>
+        <v>6458105</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122530740</v>
+        <v>122531909</v>
       </c>
       <c r="B2" t="n">
-        <v>80617</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R2" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122528135</v>
+        <v>122527769</v>
       </c>
       <c r="B3" t="n">
-        <v>8430</v>
+        <v>95015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323509</v>
+        <v>323433</v>
       </c>
       <c r="R3" t="n">
-        <v>6458215</v>
+        <v>6458170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122529772</v>
+        <v>122530740</v>
       </c>
       <c r="B4" t="n">
-        <v>95015</v>
+        <v>80617</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323743</v>
+        <v>323863</v>
       </c>
       <c r="R4" t="n">
-        <v>6458096</v>
+        <v>6457768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122531909</v>
+        <v>122532617</v>
       </c>
       <c r="B5" t="n">
-        <v>5193</v>
+        <v>95015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1002,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323645</v>
+        <v>323263</v>
       </c>
       <c r="R5" t="n">
-        <v>6457645</v>
+        <v>6457903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1208,7 +1198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122527769</v>
+        <v>122529772</v>
       </c>
       <c r="B7" t="n">
         <v>95015</v>
@@ -1244,14 +1234,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323433</v>
+        <v>323743</v>
       </c>
       <c r="R7" t="n">
-        <v>6458170</v>
+        <v>6458096</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122532617</v>
+        <v>122527780</v>
       </c>
       <c r="B8" t="n">
-        <v>95015</v>
+        <v>94655</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,34 +1316,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323263</v>
+        <v>323433</v>
       </c>
       <c r="R8" t="n">
-        <v>6457903</v>
+        <v>6458170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531091</v>
+        <v>122528135</v>
       </c>
       <c r="B10" t="n">
-        <v>57400</v>
+        <v>8430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,43 +1521,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323863</v>
+        <v>323509</v>
       </c>
       <c r="R10" t="n">
-        <v>6457768</v>
+        <v>6458215</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122527780</v>
+        <v>122531091</v>
       </c>
       <c r="B11" t="n">
-        <v>94655</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,38 +1633,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323433</v>
+        <v>323863</v>
       </c>
       <c r="R11" t="n">
-        <v>6458170</v>
+        <v>6457768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686735</v>
+        <v>122686698</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>56594</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,30 +1744,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1777,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323636</v>
+        <v>323768</v>
       </c>
       <c r="R12" t="n">
-        <v>6457620</v>
+        <v>6458043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686698</v>
+        <v>122686735</v>
       </c>
       <c r="B15" t="n">
-        <v>56594</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,29 +2089,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323768</v>
+        <v>323636</v>
       </c>
       <c r="R15" t="n">
-        <v>6458043</v>
+        <v>6457620</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,6 +2171,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122531909</v>
+        <v>122530740</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>80617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R2" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122530740</v>
+        <v>122531909</v>
       </c>
       <c r="B4" t="n">
-        <v>80617</v>
+        <v>5193</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R4" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686595</v>
+        <v>122686735</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,29 +1744,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323745</v>
+        <v>323636</v>
       </c>
       <c r="R12" t="n">
-        <v>6458102</v>
+        <v>6457620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1826,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686735</v>
+        <v>122686633</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,30 +1861,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1892,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323636</v>
+        <v>323737</v>
       </c>
       <c r="R13" t="n">
-        <v>6457620</v>
+        <v>6458105</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,7 +1942,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686633</v>
+        <v>122686698</v>
       </c>
       <c r="B14" t="n">
         <v>56688</v>
@@ -1998,7 +1998,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323737</v>
+        <v>323768</v>
       </c>
       <c r="R14" t="n">
-        <v>6458105</v>
+        <v>6458043</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686698</v>
+        <v>122686595</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323768</v>
+        <v>323745</v>
       </c>
       <c r="R15" t="n">
-        <v>6458043</v>
+        <v>6458102</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122532617</v>
+        <v>122529772</v>
       </c>
       <c r="B2" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323263</v>
+        <v>323743</v>
       </c>
       <c r="R2" t="n">
-        <v>6457903</v>
+        <v>6458096</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>122530740</v>
       </c>
       <c r="B3" t="n">
-        <v>80719</v>
+        <v>80723</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122528135</v>
+        <v>122531091</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323509</v>
+        <v>323863</v>
       </c>
       <c r="R4" t="n">
-        <v>6458215</v>
+        <v>6457768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +968,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122531091</v>
+        <v>122527780</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>94766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323863</v>
+        <v>323433</v>
       </c>
       <c r="R5" t="n">
-        <v>6457768</v>
+        <v>6458170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122527902</v>
+        <v>122527769</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,46 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323476</v>
+        <v>323433</v>
       </c>
       <c r="R6" t="n">
-        <v>6458188</v>
+        <v>6458170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122530418</v>
+        <v>122528135</v>
       </c>
       <c r="B8" t="n">
-        <v>95118</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,34 +1313,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323793</v>
+        <v>323509</v>
       </c>
       <c r="R8" t="n">
-        <v>6457779</v>
+        <v>6458215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,17 +1384,13 @@
           <t>2025-02-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1422,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122529772</v>
+        <v>122530418</v>
       </c>
       <c r="B9" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323743</v>
+        <v>323793</v>
       </c>
       <c r="R9" t="n">
-        <v>6458096</v>
+        <v>6457779</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122527769</v>
+        <v>122527902</v>
       </c>
       <c r="B10" t="n">
-        <v>95118</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,38 +1528,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323433</v>
+        <v>323476</v>
       </c>
       <c r="R10" t="n">
-        <v>6458170</v>
+        <v>6458188</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122527780</v>
+        <v>122532617</v>
       </c>
       <c r="B11" t="n">
-        <v>94758</v>
+        <v>95126</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,34 +1642,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323433</v>
+        <v>323263</v>
       </c>
       <c r="R11" t="n">
-        <v>6458170</v>
+        <v>6457903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122529772</v>
+        <v>122532617</v>
       </c>
       <c r="B2" t="n">
         <v>95126</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323743</v>
+        <v>323263</v>
       </c>
       <c r="R2" t="n">
-        <v>6458096</v>
+        <v>6457903</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122530740</v>
+        <v>122527769</v>
       </c>
       <c r="B3" t="n">
-        <v>80723</v>
+        <v>95126</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323863</v>
+        <v>323433</v>
       </c>
       <c r="R3" t="n">
-        <v>6457768</v>
+        <v>6458170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122531091</v>
+        <v>122530418</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>95126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323863</v>
+        <v>323793</v>
       </c>
       <c r="R4" t="n">
-        <v>6457768</v>
+        <v>6457779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122527780</v>
+        <v>122530740</v>
       </c>
       <c r="B5" t="n">
-        <v>94766</v>
+        <v>80723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323433</v>
+        <v>323863</v>
       </c>
       <c r="R5" t="n">
-        <v>6458170</v>
+        <v>6457768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122527769</v>
+        <v>122527780</v>
       </c>
       <c r="B6" t="n">
-        <v>95126</v>
+        <v>94766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122531909</v>
+        <v>122528135</v>
       </c>
       <c r="B7" t="n">
-        <v>5193</v>
+        <v>8430</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1206,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323645</v>
+        <v>323509</v>
       </c>
       <c r="R7" t="n">
-        <v>6457645</v>
+        <v>6458215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,6 +1283,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122528135</v>
+        <v>122529772</v>
       </c>
       <c r="B8" t="n">
-        <v>8430</v>
+        <v>95126</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,43 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323509</v>
+        <v>323743</v>
       </c>
       <c r="R8" t="n">
-        <v>6458215</v>
+        <v>6458096</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1386,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122530418</v>
+        <v>122531091</v>
       </c>
       <c r="B9" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,38 +1416,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323793</v>
+        <v>323863</v>
       </c>
       <c r="R9" t="n">
-        <v>6457779</v>
+        <v>6457768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122532617</v>
+        <v>122531909</v>
       </c>
       <c r="B11" t="n">
-        <v>95126</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,34 +1637,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323263</v>
+        <v>323645</v>
       </c>
       <c r="R11" t="n">
-        <v>6457903</v>
+        <v>6457645</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686735</v>
+        <v>122686595</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,30 +1744,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1777,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323636</v>
+        <v>323745</v>
       </c>
       <c r="R12" t="n">
-        <v>6457620</v>
+        <v>6458102</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686633</v>
+        <v>122686698</v>
       </c>
       <c r="B13" t="n">
         <v>56688</v>
@@ -1883,7 +1881,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1893,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323737</v>
+        <v>323768</v>
       </c>
       <c r="R13" t="n">
-        <v>6458105</v>
+        <v>6458043</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1931,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,10 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686698</v>
+        <v>122686735</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1976,29 +1974,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2008,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323768</v>
+        <v>323636</v>
       </c>
       <c r="R14" t="n">
-        <v>6458043</v>
+        <v>6457620</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2047,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,6 +2056,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686595</v>
+        <v>122686633</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323745</v>
+        <v>323737</v>
       </c>
       <c r="R15" t="n">
-        <v>6458102</v>
+        <v>6458105</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122532617</v>
+        <v>122531191</v>
       </c>
       <c r="B2" t="n">
-        <v>95126</v>
+        <v>80723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323263</v>
+        <v>323863</v>
       </c>
       <c r="R2" t="n">
-        <v>6457903</v>
+        <v>6457768</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122527769</v>
+        <v>122527902</v>
       </c>
       <c r="B3" t="n">
-        <v>95126</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323433</v>
+        <v>323476</v>
       </c>
       <c r="R3" t="n">
-        <v>6458170</v>
+        <v>6458188</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122530418</v>
+        <v>122529772</v>
       </c>
       <c r="B4" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323793</v>
+        <v>323743</v>
       </c>
       <c r="R4" t="n">
-        <v>6457779</v>
+        <v>6458096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122530740</v>
+        <v>122532617</v>
       </c>
       <c r="B5" t="n">
-        <v>80723</v>
+        <v>95128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1001,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323863</v>
+        <v>323263</v>
       </c>
       <c r="R5" t="n">
-        <v>6457768</v>
+        <v>6457903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122527780</v>
+        <v>122528135</v>
       </c>
       <c r="B6" t="n">
-        <v>94766</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,34 +1107,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323433</v>
+        <v>323509</v>
       </c>
       <c r="R6" t="n">
-        <v>6458170</v>
+        <v>6458215</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1184,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122528135</v>
+        <v>122527780</v>
       </c>
       <c r="B7" t="n">
-        <v>8430</v>
+        <v>94768</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,43 +1219,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323509</v>
+        <v>323433</v>
       </c>
       <c r="R7" t="n">
-        <v>6458215</v>
+        <v>6458170</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122529772</v>
+        <v>122527769</v>
       </c>
       <c r="B8" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,14 +1341,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323743</v>
+        <v>323433</v>
       </c>
       <c r="R8" t="n">
-        <v>6458096</v>
+        <v>6458170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122527902</v>
+        <v>122531909</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,20 +1526,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1545,24 +1548,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323476</v>
+        <v>323645</v>
       </c>
       <c r="R10" t="n">
-        <v>6458188</v>
+        <v>6457645</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122531909</v>
+        <v>122530418</v>
       </c>
       <c r="B11" t="n">
-        <v>5193</v>
+        <v>95128</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1637,39 +1637,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323645</v>
+        <v>323793</v>
       </c>
       <c r="R11" t="n">
-        <v>6457645</v>
+        <v>6457779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1697,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686698</v>
+        <v>122686735</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,29 +1859,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1891,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323768</v>
+        <v>323636</v>
       </c>
       <c r="R13" t="n">
-        <v>6458043</v>
+        <v>6457620</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1931,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,6 +1941,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686735</v>
+        <v>122686633</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,30 +1976,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2007,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323636</v>
+        <v>323737</v>
       </c>
       <c r="R14" t="n">
-        <v>6457620</v>
+        <v>6458105</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2047,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2057,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686633</v>
+        <v>122686698</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323737</v>
+        <v>323768</v>
       </c>
       <c r="R15" t="n">
-        <v>6458105</v>
+        <v>6458043</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122531091</v>
+        <v>122531909</v>
       </c>
       <c r="B9" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,20 +1419,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R9" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531909</v>
+        <v>122531091</v>
       </c>
       <c r="B10" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,20 +1526,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1550,7 +1550,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R10" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122531909</v>
+        <v>122531091</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,20 +1419,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323645</v>
+        <v>323863</v>
       </c>
       <c r="R9" t="n">
-        <v>6457645</v>
+        <v>6457768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531091</v>
+        <v>122531909</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>5193</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,20 +1526,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1550,7 +1550,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R10" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122531191</v>
+        <v>122531909</v>
       </c>
       <c r="B2" t="n">
-        <v>80723</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323863</v>
+        <v>323645</v>
       </c>
       <c r="R2" t="n">
-        <v>6457768</v>
+        <v>6457645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122527902</v>
+        <v>122527780</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>94768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323476</v>
+        <v>323433</v>
       </c>
       <c r="R3" t="n">
-        <v>6458188</v>
+        <v>6458170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122529772</v>
+        <v>122530418</v>
       </c>
       <c r="B4" t="n">
         <v>95128</v>
@@ -927,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323743</v>
+        <v>323793</v>
       </c>
       <c r="R4" t="n">
-        <v>6458096</v>
+        <v>6457779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122532617</v>
+        <v>122527769</v>
       </c>
       <c r="B5" t="n">
         <v>95128</v>
@@ -1025,14 +1027,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredfjället, Bredfjället, Boh</t>
+          <t>Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>323263</v>
+        <v>323433</v>
       </c>
       <c r="R5" t="n">
-        <v>6457903</v>
+        <v>6458170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122528135</v>
+        <v>122530740</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>80723</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,47 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>323509</v>
+        <v>323863</v>
       </c>
       <c r="R6" t="n">
-        <v>6458215</v>
+        <v>6457768</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122527780</v>
+        <v>122532617</v>
       </c>
       <c r="B7" t="n">
-        <v>94768</v>
+        <v>95128</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>323433</v>
+        <v>323263</v>
       </c>
       <c r="R7" t="n">
-        <v>6458170</v>
+        <v>6457903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122527769</v>
+        <v>122528135</v>
       </c>
       <c r="B8" t="n">
-        <v>95128</v>
+        <v>8430</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,34 +1313,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredfjället, Boh</t>
+          <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>323433</v>
+        <v>323509</v>
       </c>
       <c r="R8" t="n">
-        <v>6458170</v>
+        <v>6458215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,6 +1390,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1407,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122531909</v>
+        <v>122527902</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,20 +1421,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1441,21 +1443,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>323645</v>
+        <v>323476</v>
       </c>
       <c r="R9" t="n">
-        <v>6457645</v>
+        <v>6458188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122531091</v>
+        <v>122529772</v>
       </c>
       <c r="B10" t="n">
-        <v>57494</v>
+        <v>95128</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,43 +1531,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>323863</v>
+        <v>323743</v>
       </c>
       <c r="R10" t="n">
-        <v>6457768</v>
+        <v>6458096</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122530418</v>
+        <v>122531091</v>
       </c>
       <c r="B11" t="n">
-        <v>95128</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,38 +1633,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bredfjället, Bredfjället, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>323793</v>
+        <v>323863</v>
       </c>
       <c r="R11" t="n">
-        <v>6457779</v>
+        <v>6457768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ganska stora, 1-3 dm höga kuddar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686633</v>
+        <v>122686698</v>
       </c>
       <c r="B14" t="n">
         <v>56688</v>
@@ -1998,7 +1998,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323737</v>
+        <v>323768</v>
       </c>
       <c r="R14" t="n">
-        <v>6458105</v>
+        <v>6458043</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686698</v>
+        <v>122686633</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323768</v>
+        <v>323737</v>
       </c>
       <c r="R15" t="n">
-        <v>6458043</v>
+        <v>6458105</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686595</v>
+        <v>122686735</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,29 +1744,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323745</v>
+        <v>323636</v>
       </c>
       <c r="R12" t="n">
-        <v>6458102</v>
+        <v>6457620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1826,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686735</v>
+        <v>122686633</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,30 +1861,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1892,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323636</v>
+        <v>323737</v>
       </c>
       <c r="R13" t="n">
-        <v>6457620</v>
+        <v>6458105</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,7 +1942,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686698</v>
+        <v>122686595</v>
       </c>
       <c r="B14" t="n">
         <v>56688</v>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323768</v>
+        <v>323745</v>
       </c>
       <c r="R14" t="n">
-        <v>6458043</v>
+        <v>6458102</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686633</v>
+        <v>122686698</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323737</v>
+        <v>323768</v>
       </c>
       <c r="R15" t="n">
-        <v>6458105</v>
+        <v>6458043</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686735</v>
+        <v>122686595</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,30 +1744,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1777,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323636</v>
+        <v>323745</v>
       </c>
       <c r="R12" t="n">
-        <v>6457620</v>
+        <v>6458102</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,10 +1843,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686633</v>
+        <v>122686735</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,29 +1859,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1893,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323737</v>
+        <v>323636</v>
       </c>
       <c r="R13" t="n">
-        <v>6458105</v>
+        <v>6457620</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,6 +1941,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686595</v>
+        <v>122686698</v>
       </c>
       <c r="B14" t="n">
         <v>56688</v>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323745</v>
+        <v>323768</v>
       </c>
       <c r="R14" t="n">
-        <v>6458102</v>
+        <v>6458043</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686698</v>
+        <v>122686633</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323768</v>
+        <v>323737</v>
       </c>
       <c r="R15" t="n">
-        <v>6458043</v>
+        <v>6458105</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686595</v>
+        <v>122686735</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,29 +1744,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1776,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323745</v>
+        <v>323636</v>
       </c>
       <c r="R12" t="n">
-        <v>6458102</v>
+        <v>6457620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1816,7 +1817,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,6 +1826,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1843,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686735</v>
+        <v>122686633</v>
       </c>
       <c r="B13" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1859,30 +1861,29 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1892,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323636</v>
+        <v>323737</v>
       </c>
       <c r="R13" t="n">
-        <v>6457620</v>
+        <v>6458105</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,7 +1942,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686633</v>
+        <v>122686595</v>
       </c>
       <c r="B15" t="n">
         <v>56688</v>
@@ -2113,7 +2113,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323737</v>
+        <v>323745</v>
       </c>
       <c r="R15" t="n">
-        <v>6458105</v>
+        <v>6458102</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1728,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122686735</v>
+        <v>122686698</v>
       </c>
       <c r="B12" t="n">
-        <v>5193</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,30 +1744,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1777,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>323636</v>
+        <v>323768</v>
       </c>
       <c r="R12" t="n">
-        <v>6457620</v>
+        <v>6458043</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1817,7 +1816,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
+          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,7 +1825,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,7 +1843,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122686633</v>
+        <v>122686595</v>
       </c>
       <c r="B13" t="n">
         <v>56688</v>
@@ -1883,7 +1881,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1893,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>323737</v>
+        <v>323745</v>
       </c>
       <c r="R13" t="n">
-        <v>6458105</v>
+        <v>6458102</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1931,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
+          <t>Lite, vid myrkanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,7 +1958,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122686698</v>
+        <v>122686633</v>
       </c>
       <c r="B14" t="n">
         <v>56688</v>
@@ -1998,7 +1996,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2008,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>323768</v>
+        <v>323737</v>
       </c>
       <c r="R14" t="n">
-        <v>6458043</v>
+        <v>6458105</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2048,7 +2046,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 10 ex, vinterspilling.Olikåldrig, skiktad barrskog med inslag av äldre tallar här.</t>
+          <t>Relativt färsk. Stor hög under betestall och lite på ett stenblock intill.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122686595</v>
+        <v>122686735</v>
       </c>
       <c r="B15" t="n">
-        <v>56688</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,29 +2089,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2123,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>323745</v>
+        <v>323636</v>
       </c>
       <c r="R15" t="n">
-        <v>6458102</v>
+        <v>6457620</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,7 +2162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lite, vid myrkanten.</t>
+          <t>I grov, rel nyligen död gran. Relativt färska gnag.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,6 +2171,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1731,11 +1731,11 @@
         <v>122686698</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>56697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1846,11 +1846,11 @@
         <v>122686595</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>56697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1961,11 +1961,11 @@
         <v>122686633</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>56697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>122686698</v>
       </c>
       <c r="B12" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>122686595</v>
       </c>
       <c r="B13" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>122686633</v>
       </c>
       <c r="B14" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122532617</v>
+        <v>122528419</v>
       </c>
       <c r="B2" t="n">
-        <v>95128</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323263</v>
+        <v>323556</v>
       </c>
       <c r="R2" t="n">
-        <v>6457903</v>
+        <v>6458143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,6 +769,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122532617</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bredfjället, Bredfjället, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>323263</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6457903</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljung</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 266-2025 artfynd.xlsx
+++ b/artfynd/A 266-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122528419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122532617</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>